--- a/projects/edificio-ciudad-nueva/entregables/Edificio_Ciudad_Nueva_Alquileres_Rentabilidad.xlsx
+++ b/projects/edificio-ciudad-nueva/entregables/Edificio_Ciudad_Nueva_Alquileres_Rentabilidad.xlsx
@@ -10,12 +10,13 @@
   <sheets>
     <sheet name="Rentabilidad" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Ingresos_Gastos" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Proyeccion" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Plusvalia" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Alquileres_Unidad" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Conciliacion" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Datos_Originales" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Parametros" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Superficies_Valor" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Proyeccion" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Plusvalia" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Alquileres_Unidad" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Conciliacion" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Datos_Originales" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Parametros" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="284">
   <si>
     <t xml:space="preserve">Rentabilidad sobre el precio — tipo de cambio del día</t>
   </si>
@@ -95,6 +96,33 @@
     <t xml:space="preserve">Indicadores sobre el precio de venta, sin gastos de adquisición (escribanía, impuestos de transferencia, honorarios). No constituyen rentabilidad garantizada.</t>
   </si>
   <si>
+    <t xml:space="preserve">Sensibilidad al tipo de cambio (mismo ingreso en guaraníes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo de cambio (Gs/USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rent. bruta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rent. neta final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planilla original: 6.100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actualización 02/10/2026: 5.873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoy (09/10/2026): TC del día</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escenario: 6.300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los alquileres se cobran en guaraníes: si el guaraní se aprecia (TC más bajo), la renta en USD sube; si se deprecia, baja.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ingresos y egresos anuales — tipo de cambio del día</t>
   </si>
   <si>
@@ -179,6 +207,84 @@
     <t xml:space="preserve">IVA efectivo sobre el bruto</t>
   </si>
   <si>
+    <t xml:space="preserve">Superficies y valor del inmueble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terreno: frente × fondo (m²)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 × 31 = 341 m² (control aritmético).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Superficie de terreno informada (m²)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se usa la superficie informada (340 m²).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Superficie construida total (m²)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informada por el founder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Índice de construcción (m² construidos / m² de terreno)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veces la superficie del terreno.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio por m² construido (USD, terreno incluido)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio / superficie construida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio por m² de terreno (USD, construcción incluida)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio / superficie del terreno.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo de construir hoy la misma superficie (USD, sin terreno)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.109 m² × USD 650/m² (edificio de departamentos, calidad básica, obra nueva).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio / costo de construcción nueva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El precio equivale a este % del costo de levantar hoy un edificio de igual superficie, sin contar el terreno.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidades que generan renta (13 dptos. + local)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Composición comercial.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio por unidad (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio / 14 unidades.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparable: precio por unidad del edificio publicado en Ciudad Nueva (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USD 650.000 / 9 unidades (precio de oferta).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingreso bruto anual por m² construido (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingreso bruto anual / m² construidos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencias, no tasación: el edificio es usado (antigüedad no informada) y el costo de reposición no descuenta depreciación. El comparable es un precio de oferta sin superficie publicada.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Proyección de alquiler a 5 años — tres escenarios (USD, TC del día constante)</t>
   </si>
   <si>
@@ -242,7 +348,7 @@
     <t xml:space="preserve">Local comercial (desde)</t>
   </si>
   <si>
-    <t xml:space="preserve">Avisos publicados (InfoCasas, consulta 03/10/2026, categoría C): incluyen unidades más nuevas o con amenities, por lo que no son comparables directos. La brecha indica margen de ajuste en renovaciones, sujeto al estado de cada unidad.</t>
+    <t xml:space="preserve">Avisos publicados (InfoCasas, consulta 10/10/2026, categoría C): incluyen unidades más nuevas o con amenities, por lo que no son comparables directos. La brecha indica margen de ajuste en renovaciones, sujeto al estado de cada unidad.</t>
   </si>
   <si>
     <t xml:space="preserve">Plusvalía y retorno total a 5 años — tres escenarios</t>
@@ -605,16 +711,16 @@
     <t xml:space="preserve">Dato de mercado</t>
   </si>
   <si>
-    <t xml:space="preserve">Cierre del mercado interbancario del viernes 02/10/2026 (último día hábil al 03/10/2026). Fuente: BCP, Mercado Libre Fluctuante Interbancario; informado por ABC Color 02/10/2026. Casas de cambio ese día: G. 5.780 compra / G. 5.860 venta.</t>
+    <t xml:space="preserve">Cierre del mercado interbancario del viernes 09/10/2026 (último día hábil al sábado 10/10/2026): G. 5.694. Fuente: BCP, informado por ABC Color 09/10/2026 (mercado minorista ~G. 5.720). Actualización anterior: G. 5.873 (02/10/2026).</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha del tipo de cambio</t>
   </si>
   <si>
-    <t xml:space="preserve">02/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regla del founder (03/10/2026): recalcular siempre al tipo de cambio del día, aunque la planilla traiga otro.</t>
+    <t xml:space="preserve">09/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-100 (founder 03/10/2026): recalcular siempre al tipo de cambio del día, aunque la planilla traiga otro.</t>
   </si>
   <si>
     <t xml:space="preserve">Tipo de cambio de la planilla original (referencia histórica)</t>
@@ -722,7 +828,7 @@
     <t xml:space="preserve">Dato de mercado (C)</t>
   </si>
   <si>
-    <t xml:space="preserve">InfoCasas, alquiler 1 dormitorio en Ciudad Nueva, consulta 03/10/2026 (avisos, no contratos).</t>
+    <t xml:space="preserve">InfoCasas, alquiler 1 dormitorio en Ciudad Nueva, consulta 10/10/2026 (avisos, no contratos): Gs 3.000.000 (44 m²) a Gs 3.200.000 (51 m²).</t>
   </si>
   <si>
     <t xml:space="preserve">Mercado 1 dormitorio — valor alto publicado (Gs/mes)</t>
@@ -734,7 +840,7 @@
     <t xml:space="preserve">Mercado 2 dormitorios — valor bajo publicado (Gs/mes)</t>
   </si>
   <si>
-    <t xml:space="preserve">InfoCasas, alquiler 2 dormitorios en Ciudad Nueva, consulta 03/10/2026.</t>
+    <t xml:space="preserve">InfoCasas, alquiler 2 dormitorios en Ciudad Nueva, consulta 10/10/2026 (77 avisos; desde Gs 2.100.000 por 100 m²).</t>
   </si>
   <si>
     <t xml:space="preserve">Mercado 2 dormitorios — valor alto publicado (Gs/mes)</t>
@@ -743,7 +849,37 @@
     <t xml:space="preserve">Mercado local comercial — desde (Gs/mes)</t>
   </si>
   <si>
-    <t xml:space="preserve">InfoCasas, salones comerciales en Ciudad Nueva, consulta 03/10/2026.</t>
+    <t xml:space="preserve">InfoCasas, salones comerciales en Ciudad Nueva, consulta 03/10/2026 (sin cambios relevados al 10/10/2026).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frente del terreno (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founder 10/10/2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fondo del terreno (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Superficie del terreno informada (m²)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founder 10/10/2026: 340 m². Nota: 11 × 31 = 341 m² (diferencia de 1 m², redondeo de medidas; se usa la superficie informada).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo de construcción de referencia — edificio de departamentos, calidad básica (USD/m²)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">knowledge-base/investment/market-intelligence/construction-costs/06-costos-de-construccion.md (categoría A, founder 2026-08-15). Obra nueva terminada, sin terreno.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparable: edificio en venta en Ciudad Nueva (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfoCasas Ref #GB49D6: edificio de 5 niveles y 9 unidades en Ciudad Nueva, consulta 10/10/2026 (precio de oferta; superficie no publicada).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparable: unidades del edificio publicado</t>
   </si>
 </sst>
 </file>
@@ -757,11 +893,11 @@
     <numFmt numFmtId="167" formatCode="&quot;USD &quot;#,##0.00"/>
     <numFmt numFmtId="168" formatCode="&quot;₲ &quot;#,##0"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
-    <numFmt numFmtId="170" formatCode="0"/>
+    <numFmt numFmtId="170" formatCode="#,##0"/>
     <numFmt numFmtId="171" formatCode="&quot;USD &quot;#,##0"/>
     <numFmt numFmtId="172" formatCode="0%"/>
-    <numFmt numFmtId="173" formatCode="0;\-0;0"/>
-    <numFmt numFmtId="174" formatCode="#,##0"/>
+    <numFmt numFmtId="173" formatCode="0"/>
+    <numFmt numFmtId="174" formatCode="0;\-0;0"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -910,7 +1046,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -971,11 +1107,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -991,11 +1139,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1023,11 +1167,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1039,7 +1179,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1056,6 +1196,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1311,7 +1455,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="56"/>
@@ -1346,7 +1490,7 @@
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">Ingresos_Gastos!$B$7/Parametros!$B$5</f>
-        <v>0.117486804018389</v>
+        <v>0.12118018967334</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>6</v>
@@ -1358,7 +1502,7 @@
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">Ingresos_Gastos!$B$13/Parametros!$B$5</f>
-        <v>0.0887142556665098</v>
+        <v>0.0916140829355978</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>8</v>
@@ -1370,7 +1514,7 @@
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">Ingresos_Gastos!$B$15/Parametros!$B$5</f>
-        <v>0.0798428300998588</v>
+        <v>0.082452674642038</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>10</v>
@@ -1382,7 +1526,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">Parametros!$B$5/Ingresos_Gastos!$B$7</f>
-        <v>8.51159420289855</v>
+        <v>8.25217391304348</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>12</v>
@@ -1394,7 +1538,7 @@
       </c>
       <c r="B9" s="8" t="n">
         <f aca="false">Ingresos_Gastos!$B$15/12</f>
-        <v>2262.213519496</v>
+        <v>2336.15911485774</v>
       </c>
       <c r="C9" s="6"/>
     </row>
@@ -1450,6 +1594,79 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <f aca="false">Alquileres_Unidad!$H$20*12/6100/Parametros!$B$5</f>
+        <v>0.113114754098361</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <f aca="false">((Alquileres_Unidad!$H$20*12/6100)*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)/Parametros!$B$5</f>
+        <v>0.0767534233365477</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <f aca="false">Alquileres_Unidad!$H$20*12/5873/Parametros!$B$5</f>
+        <v>0.117486804018389</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <f aca="false">((Alquileres_Unidad!$H$20*12/5873)*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)/Parametros!$B$5</f>
+        <v>0.0798428300998588</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <f aca="false">Alquileres_Unidad!$H$20*12/Parametros!$B$6/Parametros!$B$5</f>
+        <v>0.12118018967334</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <f aca="false">((Alquileres_Unidad!$H$20*12/Parametros!$B$6)*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)/Parametros!$B$5</f>
+        <v>0.0824526746420381</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <f aca="false">Alquileres_Unidad!$H$20*12/6300/Parametros!$B$5</f>
+        <v>0.10952380952381</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <f aca="false">((Alquileres_Unidad!$H$20*12/6300)*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)/Parametros!$B$5</f>
+        <v>0.0742159663865546</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1479,7 +1696,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1489,13 +1706,13 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>4</v>
@@ -1503,111 +1720,111 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">Alquileres_Unidad!$H$20</f>
         <v>19550000</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B6" s="12" t="n">
         <f aca="false">B5/Parametros!$B$6</f>
-        <v>3328.79278052103</v>
+        <v>3433.43870741131</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B7" s="13" t="n">
         <f aca="false">B6*12</f>
-        <v>39945.5133662523</v>
+        <v>41201.2644889357</v>
       </c>
       <c r="C7" s="14" t="n">
         <f aca="false">B7/$B$7</f>
         <v>1</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B8" s="12" t="n">
         <f aca="false">-Alquileres_Unidad!$J$20*12/Parametros!$B$6</f>
-        <v>-2191.38430103865</v>
+        <v>-2260.27397260274</v>
       </c>
       <c r="C8" s="14" t="n">
         <f aca="false">-B8/$B$7</f>
         <v>0.0548593350383632</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B9" s="12" t="n">
         <f aca="false">-B7*Parametros!$B$11</f>
-        <v>-1198.36540098757</v>
+        <v>-1236.03793466807</v>
       </c>
       <c r="C9" s="14" t="n">
         <f aca="false">-B9/$B$7</f>
         <v>0.03</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B10" s="12" t="n">
         <f aca="false">-B7*Parametros!$B$12</f>
-        <v>-3195.64106930019</v>
+        <v>-3296.10115911486</v>
       </c>
       <c r="C10" s="14" t="n">
         <f aca="false">-B10/$B$7</f>
         <v>0.08</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B11" s="12" t="n">
         <f aca="false">-B7*Parametros!$B$13</f>
-        <v>-1997.27566831262</v>
+        <v>-2060.06322444679</v>
       </c>
       <c r="C11" s="14" t="n">
         <f aca="false">-B11/$B$7</f>
         <v>0.05</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">-Parametros!$B$14</f>
@@ -1615,72 +1832,72 @@
       </c>
       <c r="C12" s="14" t="n">
         <f aca="false">-B12/$B$7</f>
-        <v>0.0300409207161125</v>
+        <v>0.0291253196930946</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B13" s="13" t="n">
         <f aca="false">SUM(B7:B12)</f>
-        <v>30162.8469266133</v>
+        <v>31148.7881981033</v>
       </c>
       <c r="C13" s="14" t="n">
         <f aca="false">B13/$B$7</f>
-        <v>0.755099744245524</v>
+        <v>0.756015345268542</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B14" s="12" t="n">
         <f aca="false">-B13*Parametros!$B$15</f>
-        <v>-3016.28469266133</v>
+        <v>-3114.87881981033</v>
       </c>
       <c r="C14" s="14" t="n">
         <f aca="false">-B14/$B$7</f>
-        <v>0.0755099744245524</v>
+        <v>0.0756015345268542</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B15" s="13" t="n">
         <f aca="false">B13+B14</f>
-        <v>27146.562233952</v>
+        <v>28033.9093782929</v>
       </c>
       <c r="C15" s="14" t="n">
         <f aca="false">B15/$B$7</f>
-        <v>0.679589769820972</v>
+        <v>0.680413810741688</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B17" s="8" t="n">
         <f aca="false">B15/12</f>
-        <v>2262.213519496</v>
+        <v>2336.15911485774</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B18" s="5" t="n">
         <f aca="false">-B8/B7</f>
@@ -1703,16 +1920,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1722,311 +1940,161 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="16" t="n">
-        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$17)^(A5-1)</f>
-        <v>39945.5133662523</v>
-      </c>
-      <c r="C5" s="16" t="n">
-        <f aca="false">(B5*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
-        <v>27146.562233952</v>
-      </c>
-      <c r="D5" s="16" t="n">
-        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$18)^(A5-1)</f>
-        <v>39945.5133662523</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <f aca="false">(D5*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
-        <v>27146.562233952</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$19)^(A5-1)</f>
-        <v>39945.5133662523</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <f aca="false">(F5*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
-        <v>27146.562233952</v>
+      <c r="A5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="15" t="n">
+        <f aca="false">Parametros!$B$28*Parametros!$B$29</f>
+        <v>341</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="16" t="n">
-        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$17)^(A6-1)</f>
-        <v>41143.8787672399</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <f aca="false">(B6*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
-        <v>27993.3591009705</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$18)^(A6-1)</f>
-        <v>41942.789034565</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <f aca="false">(D6*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
-        <v>28557.8903456496</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$19)^(A6-1)</f>
-        <v>43141.1544355525</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <f aca="false">(F6*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
-        <v>29404.6872126681</v>
+      <c r="A6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <f aca="false">Parametros!$B$30</f>
+        <v>340</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="16" t="n">
-        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$17)^(A7-1)</f>
-        <v>42378.1951302571</v>
-      </c>
-      <c r="C7" s="16" t="n">
-        <f aca="false">(B7*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
-        <v>28865.5598739997</v>
-      </c>
-      <c r="D7" s="16" t="n">
-        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$18)^(A7-1)</f>
-        <v>44039.9284862932</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <f aca="false">(D7*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
-        <v>30039.7848629321</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$19)^(A7-1)</f>
-        <v>46592.4467903967</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <f aca="false">(F7*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
-        <v>31843.4621896816</v>
+      <c r="A7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="15" t="n">
+        <f aca="false">Parametros!$B$31</f>
+        <v>1109</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="16" t="n">
-        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$17)^(A8-1)</f>
-        <v>43649.5409841648</v>
-      </c>
-      <c r="C8" s="16" t="n">
-        <f aca="false">(B8*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
-        <v>29763.9266702197</v>
-      </c>
-      <c r="D8" s="16" t="n">
-        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$18)^(A8-1)</f>
-        <v>46241.9249106079</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <f aca="false">(D8*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
-        <v>31595.7741060787</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$19)^(A8-1)</f>
-        <v>50319.8425336285</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <f aca="false">(F8*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
-        <v>34477.3391648561</v>
+      <c r="A8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <f aca="false">B7/B6</f>
+        <v>3.26176470588235</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="16" t="n">
-        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$17)^(A9-1)</f>
-        <v>44959.0272136898</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <f aca="false">(B9*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
-        <v>30689.2444703262</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$18)^(A9-1)</f>
-        <v>48554.0211561383</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <f aca="false">(D9*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
-        <v>33229.5628113826</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$19)^(A9-1)</f>
-        <v>54345.4299363188</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <f aca="false">(F9*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
-        <v>37321.9262980446</v>
+      <c r="A9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <f aca="false">Parametros!$B$5/B7</f>
+        <v>306.582506762849</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="17" t="n">
-        <f aca="false">SUM(B5:B9)</f>
-        <v>212076.155461604</v>
-      </c>
-      <c r="C10" s="17" t="n">
-        <f aca="false">SUM(C5:C9)</f>
-        <v>144458.652349468</v>
-      </c>
-      <c r="D10" s="17" t="n">
-        <f aca="false">SUM(D5:D9)</f>
-        <v>220724.176953857</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <f aca="false">SUM(E5:E9)</f>
-        <v>150569.574359995</v>
-      </c>
-      <c r="F10" s="17" t="n">
-        <f aca="false">SUM(F5:F9)</f>
-        <v>234344.387062149</v>
-      </c>
-      <c r="G10" s="17" t="n">
-        <f aca="false">SUM(G5:G9)</f>
-        <v>160193.977099203</v>
+        <v>70</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <f aca="false">Parametros!$B$5/B6</f>
+        <v>1000</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="18" t="n">
-        <f aca="false">Parametros!$B$17</f>
-        <v>0.03</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <f aca="false">Parametros!$B$18</f>
-        <v>0.05</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <f aca="false">Parametros!$B$19</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G15" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="B11" s="16" t="n">
+        <f aca="false">B7*Parametros!$B$32</f>
+        <v>720850</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <f aca="false">Parametros!$B$5/B11</f>
+        <v>0.471665395019768</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="16" t="n">
+        <f aca="false">Parametros!$B$5/B13</f>
+        <v>24285.7142857143</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="16" t="n">
+        <f aca="false">Parametros!$B$33/Parametros!$B$34</f>
+        <v>72222.2222222222</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="19" t="n">
-        <f aca="false">AVERAGEIFS(Alquileres_Unidad!$H$5:$H$19,Alquileres_Unidad!$E$5:$E$19,"1 dormitorio")</f>
-        <v>1158333.33333333</v>
-      </c>
-      <c r="C16" s="11" t="n">
-        <f aca="false">Parametros!$B$23</f>
-        <v>2500000</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <f aca="false">Parametros!$B$24</f>
-        <v>3000000</v>
-      </c>
-      <c r="E16" s="20" t="n">
-        <f aca="false">C16/B16-1</f>
-        <v>1.15827338129496</v>
-      </c>
-      <c r="F16" s="21" t="n">
-        <f aca="false">COUNTIFS(Alquileres_Unidad!$E$5:$E$19,"1 dormitorio")</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" s="19" t="n">
-        <f aca="false">AVERAGEIFS(Alquileres_Unidad!$H$5:$H$19,Alquileres_Unidad!$E$5:$E$19,"2 dormitorios")</f>
-        <v>1516666.66666667</v>
-      </c>
-      <c r="C17" s="11" t="n">
-        <f aca="false">Parametros!$B$25</f>
-        <v>2100000</v>
-      </c>
-      <c r="D17" s="11" t="n">
-        <f aca="false">Parametros!$B$26</f>
-        <v>4200000</v>
-      </c>
-      <c r="E17" s="20" t="n">
-        <f aca="false">C17/B17-1</f>
-        <v>0.384615384615385</v>
-      </c>
-      <c r="F17" s="21" t="n">
-        <f aca="false">COUNTIFS(Alquileres_Unidad!$E$5:$E$19,"2 dormitorios")</f>
-        <v>6</v>
+        <v>82</v>
+      </c>
+      <c r="B16" s="8" t="n">
+        <f aca="false">Ingresos_Gastos!$B$7/B7</f>
+        <v>37.1517263200502</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="11" t="n">
-        <f aca="false">Parametros!$B$27</f>
-        <v>2700000</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>71</v>
+      <c r="A18" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2045,16 +2113,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2064,264 +2132,311 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>75</v>
+        <v>89</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="18" t="n">
-        <f aca="false">Parametros!$B$20</f>
-        <v>0.02</v>
-      </c>
-      <c r="C5" s="18" t="n">
-        <f aca="false">Parametros!$B$21</f>
-        <v>0.035</v>
-      </c>
-      <c r="D5" s="18" t="n">
-        <f aca="false">Parametros!$B$22</f>
-        <v>0.05</v>
+      <c r="A5" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="16" t="n">
+        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$17)^(A5-1)</f>
+        <v>41201.2644889357</v>
+      </c>
+      <c r="C5" s="16" t="n">
+        <f aca="false">(B5*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
+        <v>28033.9093782929</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$18)^(A5-1)</f>
+        <v>41201.2644889357</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <f aca="false">(D5*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
+        <v>28033.9093782929</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$19)^(A5-1)</f>
+        <v>41201.2644889357</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <f aca="false">(F5*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
+        <v>28033.9093782929</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>77</v>
+      <c r="A6" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B6" s="16" t="n">
-        <f aca="false">Parametros!$B$5*(1+B5)^5</f>
-        <v>375387.473088</v>
+        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$17)^(A6-1)</f>
+        <v>42437.3024236038</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">Parametros!$B$5*(1+C5)^5</f>
-        <v>403813.343919937</v>
+        <f aca="false">(B6*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
+        <v>28907.3266596417</v>
       </c>
       <c r="D6" s="16" t="n">
-        <f aca="false">Parametros!$B$5*(1+D5)^5</f>
-        <v>433935.73125</v>
+        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$18)^(A6-1)</f>
+        <v>43261.3277133825</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <f aca="false">(D6*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
+        <v>29489.6048472076</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$19)^(A6-1)</f>
+        <v>44497.3656480506</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <f aca="false">(F6*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
+        <v>30363.0221285564</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>78</v>
+      <c r="A7" s="19" t="n">
+        <v>3</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">B6-Parametros!$B$5</f>
-        <v>35387.473088</v>
+        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$17)^(A7-1)</f>
+        <v>43710.4214963119</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">C6-Parametros!$B$5</f>
-        <v>63813.3439199373</v>
+        <f aca="false">(B7*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
+        <v>29806.946459431</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">D6-Parametros!$B$5</f>
-        <v>93935.7312500001</v>
+        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$18)^(A7-1)</f>
+        <v>45424.3940990516</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <f aca="false">(D7*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
+        <v>31018.085089568</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$19)^(A7-1)</f>
+        <v>48057.1548998946</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <f aca="false">(F7*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
+        <v>32878.4638988409</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>79</v>
+      <c r="A8" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">-B6*Parametros!$B$16</f>
-        <v>-5630.81209632</v>
+        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$17)^(A8-1)</f>
+        <v>45021.7341412013</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">-C6*Parametros!$B$16</f>
-        <v>-6057.20015879906</v>
+        <f aca="false">(B8*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
+        <v>30733.5548532139</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">-D6*Parametros!$B$16</f>
-        <v>-6509.03596875</v>
+        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$18)^(A8-1)</f>
+        <v>47695.6138040042</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <f aca="false">(D8*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
+        <v>32622.9893440464</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$19)^(A8-1)</f>
+        <v>51901.7272918862</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <f aca="false">(F8*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
+        <v>35595.1410107482</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="22" t="n">
-        <f aca="false">Proyeccion!C10</f>
-        <v>144458.652349468</v>
-      </c>
-      <c r="C9" s="22" t="n">
-        <f aca="false">Proyeccion!E10</f>
-        <v>150569.574359995</v>
-      </c>
-      <c r="D9" s="22" t="n">
-        <f aca="false">Proyeccion!G10</f>
-        <v>160193.977099203</v>
+      <c r="A9" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$17)^(A9-1)</f>
+        <v>46372.3861654373</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <f aca="false">(B9*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
+        <v>31687.9614988103</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$18)^(A9-1)</f>
+        <v>50080.3944942044</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <f aca="false">(D9*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
+        <v>34308.1388112487</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <f aca="false">Ingresos_Gastos!$B$7*(1+Parametros!$B$19)^(A9-1)</f>
+        <v>56053.8654752371</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <f aca="false">(F9*(1-Ingresos_Gastos!$B$18-Parametros!$B$11-Parametros!$B$12-Parametros!$B$13)-Parametros!$B$14)*(1-Parametros!$B$15)</f>
+        <v>38529.152291608</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="17" t="n">
-        <f aca="false">B7+B8+B9</f>
-        <v>174215.313341148</v>
-      </c>
-      <c r="C10" s="17" t="n">
-        <f aca="false">C7+C8+C9</f>
-        <v>208325.718121133</v>
-      </c>
-      <c r="D10" s="17" t="n">
-        <f aca="false">D7+D8+D9</f>
-        <v>247620.672380453</v>
+        <v>93</v>
+      </c>
+      <c r="B10" s="20" t="n">
+        <f aca="false">SUM(B5:B9)</f>
+        <v>218743.10871549</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <f aca="false">SUM(C5:C9)</f>
+        <v>149169.69884939</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <f aca="false">SUM(D5:D9)</f>
+        <v>227662.994599579</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <f aca="false">SUM(E5:E9)</f>
+        <v>155472.727470364</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <f aca="false">SUM(F5:F9)</f>
+        <v>241711.377804004</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <f aca="false">SUM(G5:G9)</f>
+        <v>165399.688708046</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B11" s="14" t="n">
-        <f aca="false">B10/Parametros!$B$5</f>
-        <v>0.512397980415142</v>
-      </c>
-      <c r="C11" s="14" t="n">
-        <f aca="false">C10/Parametros!$B$5</f>
-        <v>0.612722700356274</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <f aca="false">D10/Parametros!$B$5</f>
-        <v>0.728296095236625</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="16" t="n">
-        <f aca="false">-Parametros!$B$5</f>
-        <v>-340000</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <f aca="false">-Parametros!$B$5</f>
-        <v>-340000</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <f aca="false">-Parametros!$B$5</f>
-        <v>-340000</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="16" t="n">
-        <f aca="false">Proyeccion!C5</f>
-        <v>27146.562233952</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <f aca="false">Proyeccion!E5</f>
-        <v>27146.562233952</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <f aca="false">Proyeccion!G5</f>
-        <v>27146.562233952</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="B11" s="21" t="n">
+        <f aca="false">Parametros!$B$17</f>
+        <v>0.03</v>
+      </c>
+      <c r="D11" s="21" t="n">
+        <f aca="false">Parametros!$B$18</f>
+        <v>0.05</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <f aca="false">Parametros!$B$19</f>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="16" t="n">
-        <f aca="false">Proyeccion!C6</f>
-        <v>27993.3591009705</v>
-      </c>
-      <c r="C16" s="16" t="n">
-        <f aca="false">Proyeccion!E6</f>
-        <v>28557.8903456496</v>
-      </c>
-      <c r="D16" s="16" t="n">
-        <f aca="false">Proyeccion!G6</f>
-        <v>29404.6872126681</v>
+        <v>103</v>
+      </c>
+      <c r="B16" s="22" t="n">
+        <f aca="false">AVERAGEIFS(Alquileres_Unidad!$H$5:$H$19,Alquileres_Unidad!$E$5:$E$19,"1 dormitorio")</f>
+        <v>1158333.33333333</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <f aca="false">Parametros!$B$23</f>
+        <v>3000000</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <f aca="false">Parametros!$B$24</f>
+        <v>3200000</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <f aca="false">C16/B16-1</f>
+        <v>1.58992805755396</v>
+      </c>
+      <c r="F16" s="23" t="n">
+        <f aca="false">COUNTIFS(Alquileres_Unidad!$E$5:$E$19,"1 dormitorio")</f>
+        <v>6</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="16" t="n">
-        <f aca="false">Proyeccion!C7</f>
-        <v>28865.5598739997</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <f aca="false">Proyeccion!E7</f>
-        <v>30039.7848629321</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <f aca="false">Proyeccion!G7</f>
-        <v>31843.4621896816</v>
+        <v>104</v>
+      </c>
+      <c r="B17" s="22" t="n">
+        <f aca="false">AVERAGEIFS(Alquileres_Unidad!$H$5:$H$19,Alquileres_Unidad!$E$5:$E$19,"2 dormitorios")</f>
+        <v>1516666.66666667</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <f aca="false">Parametros!$B$25</f>
+        <v>2100000</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <f aca="false">Parametros!$B$26</f>
+        <v>6300000</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <f aca="false">C17/B17-1</f>
+        <v>0.384615384615385</v>
+      </c>
+      <c r="F17" s="23" t="n">
+        <f aca="false">COUNTIFS(Alquileres_Unidad!$E$5:$E$19,"2 dormitorios")</f>
+        <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="16" t="n">
-        <f aca="false">Proyeccion!C8</f>
-        <v>29763.9266702197</v>
-      </c>
-      <c r="C18" s="16" t="n">
-        <f aca="false">Proyeccion!E8</f>
-        <v>31595.7741060787</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <f aca="false">Proyeccion!G8</f>
-        <v>34477.3391648561</v>
+        <v>105</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <f aca="false">Parametros!$B$27</f>
+        <v>2700000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" s="16" t="n">
-        <f aca="false">Proyeccion!C9+B6+B8</f>
-        <v>400445.905462006</v>
-      </c>
-      <c r="C19" s="16" t="n">
-        <f aca="false">Proyeccion!E9+C6+C8</f>
-        <v>430985.706572521</v>
-      </c>
-      <c r="D19" s="16" t="n">
-        <f aca="false">Proyeccion!G9+D6+D8</f>
-        <v>464748.621579295</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="23" t="n">
-        <f aca="false">IRR(B14:B19)</f>
-        <v>0.0988551536777681</v>
-      </c>
-      <c r="C20" s="23" t="n">
-        <f aca="false">IRR(C14:C19)</f>
-        <v>0.114632580761375</v>
-      </c>
-      <c r="D20" s="23" t="n">
-        <f aca="false">IRR(D14:D19)</f>
-        <v>0.131925549621216</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>91</v>
+      <c r="A19" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2336,6 +2451,301 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" s="21" t="n">
+        <f aca="false">Parametros!$B$20</f>
+        <v>0.02</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <f aca="false">Parametros!$B$21</f>
+        <v>0.035</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <f aca="false">Parametros!$B$22</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="16" t="n">
+        <f aca="false">Parametros!$B$5*(1+B5)^5</f>
+        <v>375387.473088</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <f aca="false">Parametros!$B$5*(1+C5)^5</f>
+        <v>403813.343919937</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <f aca="false">Parametros!$B$5*(1+D5)^5</f>
+        <v>433935.73125</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="16" t="n">
+        <f aca="false">B6-Parametros!$B$5</f>
+        <v>35387.473088</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <f aca="false">C6-Parametros!$B$5</f>
+        <v>63813.3439199373</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <f aca="false">D6-Parametros!$B$5</f>
+        <v>93935.7312500001</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <f aca="false">-B6*Parametros!$B$16</f>
+        <v>-5630.81209632</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <f aca="false">-C6*Parametros!$B$16</f>
+        <v>-6057.20015879906</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <f aca="false">-D6*Parametros!$B$16</f>
+        <v>-6509.03596875</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <f aca="false">Proyeccion!C10</f>
+        <v>149169.69884939</v>
+      </c>
+      <c r="C9" s="24" t="n">
+        <f aca="false">Proyeccion!E10</f>
+        <v>155472.727470364</v>
+      </c>
+      <c r="D9" s="24" t="n">
+        <f aca="false">Proyeccion!G10</f>
+        <v>165399.688708046</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="20" t="n">
+        <f aca="false">B7+B8+B9</f>
+        <v>178926.35984107</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <f aca="false">C7+C8+C9</f>
+        <v>213228.871231502</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <f aca="false">D7+D8+D9</f>
+        <v>252826.383989297</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" s="14" t="n">
+        <f aca="false">B10/Parametros!$B$5</f>
+        <v>0.526253999532559</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <f aca="false">C10/Parametros!$B$5</f>
+        <v>0.627143738916182</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <f aca="false">D10/Parametros!$B$5</f>
+        <v>0.743607011733225</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="16" t="n">
+        <f aca="false">-Parametros!$B$5</f>
+        <v>-340000</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <f aca="false">-Parametros!$B$5</f>
+        <v>-340000</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <f aca="false">-Parametros!$B$5</f>
+        <v>-340000</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" s="16" t="n">
+        <f aca="false">Proyeccion!C5</f>
+        <v>28033.9093782929</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <f aca="false">Proyeccion!E5</f>
+        <v>28033.9093782929</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <f aca="false">Proyeccion!G5</f>
+        <v>28033.9093782929</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" s="16" t="n">
+        <f aca="false">Proyeccion!C6</f>
+        <v>28907.3266596417</v>
+      </c>
+      <c r="C16" s="16" t="n">
+        <f aca="false">Proyeccion!E6</f>
+        <v>29489.6048472076</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <f aca="false">Proyeccion!G6</f>
+        <v>30363.0221285564</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="16" t="n">
+        <f aca="false">Proyeccion!C7</f>
+        <v>29806.946459431</v>
+      </c>
+      <c r="C17" s="16" t="n">
+        <f aca="false">Proyeccion!E7</f>
+        <v>31018.085089568</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <f aca="false">Proyeccion!G7</f>
+        <v>32878.4638988409</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="16" t="n">
+        <f aca="false">Proyeccion!C8</f>
+        <v>30733.5548532139</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <f aca="false">Proyeccion!E8</f>
+        <v>32622.9893440464</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <f aca="false">Proyeccion!G8</f>
+        <v>35595.1410107482</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="16" t="n">
+        <f aca="false">Proyeccion!C9+B6+B8</f>
+        <v>401444.62249049</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <f aca="false">Proyeccion!E9+C6+C8</f>
+        <v>432064.282572387</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <f aca="false">Proyeccion!G9+D6+D8</f>
+        <v>465955.847572858</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="25" t="n">
+        <f aca="false">IRR(B14:B19)</f>
+        <v>0.101522066028479</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <f aca="false">IRR(C14:C19)</f>
+        <v>0.117320668447714</v>
+      </c>
+      <c r="D20" s="25" t="n">
+        <f aca="false">IRR(D14:D19)</f>
+        <v>0.134678276622818</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2358,7 +2768,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2368,37 +2778,37 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>15</v>
@@ -2409,37 +2819,37 @@
         <v>1</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D5" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>69</v>
-      </c>
       <c r="F5" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="G5" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="G5" s="27" t="n">
         <f aca="false">IF(F5="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
         <v>0.05</v>
       </c>
-      <c r="H5" s="26" t="n">
+      <c r="H5" s="28" t="n">
         <v>1500000</v>
       </c>
       <c r="I5" s="12" t="n">
         <f aca="false">H5/Parametros!$B$6</f>
-        <v>255.406095692151</v>
-      </c>
-      <c r="J5" s="19" t="n">
+        <v>263.435194942044</v>
+      </c>
+      <c r="J5" s="22" t="n">
         <f aca="false">H5*G5</f>
         <v>75000</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L5" s="6"/>
     </row>
@@ -2448,37 +2858,37 @@
         <v>2</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D6" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>69</v>
-      </c>
       <c r="F6" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="G6" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="G6" s="27" t="n">
         <f aca="false">IF(F6="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
         <v>0.05</v>
       </c>
-      <c r="H6" s="26" t="n">
+      <c r="H6" s="28" t="n">
         <v>1500000</v>
       </c>
       <c r="I6" s="12" t="n">
         <f aca="false">H6/Parametros!$B$6</f>
-        <v>255.406095692151</v>
-      </c>
-      <c r="J6" s="19" t="n">
+        <v>263.435194942044</v>
+      </c>
+      <c r="J6" s="22" t="n">
         <f aca="false">H6*G6</f>
         <v>75000</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L6" s="6"/>
     </row>
@@ -2487,37 +2897,37 @@
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="C7" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="D7" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>68</v>
-      </c>
       <c r="F7" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="G7" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="G7" s="27" t="n">
         <f aca="false">IF(F7="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
         <v>0.05</v>
       </c>
-      <c r="H7" s="26" t="n">
+      <c r="H7" s="28" t="n">
         <v>1200000</v>
       </c>
       <c r="I7" s="12" t="n">
         <f aca="false">H7/Parametros!$B$6</f>
-        <v>204.32487655372</v>
-      </c>
-      <c r="J7" s="19" t="n">
+        <v>210.748155953635</v>
+      </c>
+      <c r="J7" s="22" t="n">
         <f aca="false">H7*G7</f>
         <v>60000</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L7" s="6"/>
     </row>
@@ -2526,37 +2936,37 @@
         <v>4</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="C8" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>68</v>
-      </c>
       <c r="F8" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="G8" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="G8" s="27" t="n">
         <f aca="false">IF(F8="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
         <v>0.05</v>
       </c>
-      <c r="H8" s="26" t="n">
+      <c r="H8" s="28" t="n">
         <v>1100000</v>
       </c>
       <c r="I8" s="12" t="n">
         <f aca="false">H8/Parametros!$B$6</f>
-        <v>187.297803507577</v>
-      </c>
-      <c r="J8" s="19" t="n">
+        <v>193.185809624166</v>
+      </c>
+      <c r="J8" s="22" t="n">
         <f aca="false">H8*G8</f>
         <v>55000</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L8" s="6"/>
     </row>
@@ -2565,37 +2975,37 @@
         <v>5</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="E9" s="10" t="s">
-        <v>69</v>
-      </c>
       <c r="F9" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="G9" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="G9" s="27" t="n">
         <f aca="false">IF(F9="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
         <v>0.05</v>
       </c>
-      <c r="H9" s="26" t="n">
+      <c r="H9" s="28" t="n">
         <v>1600000</v>
       </c>
       <c r="I9" s="12" t="n">
         <f aca="false">H9/Parametros!$B$6</f>
-        <v>272.433168738294</v>
-      </c>
-      <c r="J9" s="19" t="n">
+        <v>280.997541271514</v>
+      </c>
+      <c r="J9" s="22" t="n">
         <f aca="false">H9*G9</f>
         <v>80000</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L9" s="6"/>
     </row>
@@ -2604,37 +3014,37 @@
         <v>6</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>69</v>
-      </c>
       <c r="F10" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="G10" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="G10" s="27" t="n">
         <f aca="false">IF(F10="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
         <v>0.05</v>
       </c>
-      <c r="H10" s="26" t="n">
+      <c r="H10" s="28" t="n">
         <v>1500000</v>
       </c>
       <c r="I10" s="12" t="n">
         <f aca="false">H10/Parametros!$B$6</f>
-        <v>255.406095692151</v>
-      </c>
-      <c r="J10" s="19" t="n">
+        <v>263.435194942044</v>
+      </c>
+      <c r="J10" s="22" t="n">
         <f aca="false">H10*G10</f>
         <v>75000</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L10" s="6"/>
     </row>
@@ -2643,37 +3053,37 @@
         <v>7</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>69</v>
-      </c>
       <c r="F11" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="G11" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="G11" s="27" t="n">
         <f aca="false">IF(F11="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
         <v>0.05</v>
       </c>
-      <c r="H11" s="26" t="n">
+      <c r="H11" s="28" t="n">
         <v>1500000</v>
       </c>
       <c r="I11" s="12" t="n">
         <f aca="false">H11/Parametros!$B$6</f>
-        <v>255.406095692151</v>
-      </c>
-      <c r="J11" s="19" t="n">
+        <v>263.435194942044</v>
+      </c>
+      <c r="J11" s="22" t="n">
         <f aca="false">H11*G11</f>
         <v>75000</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L11" s="6"/>
     </row>
@@ -2682,37 +3092,37 @@
         <v>8</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>69</v>
-      </c>
       <c r="F12" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="G12" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="G12" s="27" t="n">
         <f aca="false">IF(F12="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
         <v>0.05</v>
       </c>
-      <c r="H12" s="26" t="n">
+      <c r="H12" s="28" t="n">
         <v>1500000</v>
       </c>
       <c r="I12" s="12" t="n">
         <f aca="false">H12/Parametros!$B$6</f>
-        <v>255.406095692151</v>
-      </c>
-      <c r="J12" s="19" t="n">
+        <v>263.435194942044</v>
+      </c>
+      <c r="J12" s="22" t="n">
         <f aca="false">H12*G12</f>
         <v>75000</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L12" s="6"/>
     </row>
@@ -2721,37 +3131,37 @@
         <v>9</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>109</v>
+        <v>147</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>144</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="G13" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="G13" s="27" t="n">
         <f aca="false">IF(F13="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
         <v>0.05</v>
       </c>
-      <c r="H13" s="26" t="n">
+      <c r="H13" s="28" t="n">
         <v>1250000</v>
       </c>
       <c r="I13" s="12" t="n">
         <f aca="false">H13/Parametros!$B$6</f>
-        <v>212.838413076792</v>
-      </c>
-      <c r="J13" s="19" t="n">
+        <v>219.52932911837</v>
+      </c>
+      <c r="J13" s="22" t="n">
         <f aca="false">H13*G13</f>
         <v>62500</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L13" s="6"/>
     </row>
@@ -2760,37 +3170,37 @@
         <v>10</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>109</v>
+        <v>153</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>144</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="G14" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="G14" s="27" t="n">
         <f aca="false">IF(F14="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
         <v>0.05</v>
       </c>
-      <c r="H14" s="26" t="n">
+      <c r="H14" s="28" t="n">
         <v>1300000</v>
       </c>
       <c r="I14" s="12" t="n">
         <f aca="false">H14/Parametros!$B$6</f>
-        <v>221.351949599864</v>
-      </c>
-      <c r="J14" s="19" t="n">
+        <v>228.310502283105</v>
+      </c>
+      <c r="J14" s="22" t="n">
         <f aca="false">H14*G14</f>
         <v>65000</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L14" s="6"/>
     </row>
@@ -2799,37 +3209,37 @@
         <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>120</v>
+        <v>153</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>155</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="G15" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="G15" s="27" t="n">
         <f aca="false">IF(F15="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
         <v>0.05</v>
       </c>
-      <c r="H15" s="26" t="n">
+      <c r="H15" s="28" t="n">
         <v>1600000</v>
       </c>
       <c r="I15" s="12" t="n">
         <f aca="false">H15/Parametros!$B$6</f>
-        <v>272.433168738294</v>
-      </c>
-      <c r="J15" s="19" t="n">
+        <v>280.997541271514</v>
+      </c>
+      <c r="J15" s="22" t="n">
         <f aca="false">H15*G15</f>
         <v>80000</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L15" s="6"/>
     </row>
@@ -2838,37 +3248,37 @@
         <v>12</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>109</v>
+        <v>158</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>144</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="G16" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="G16" s="27" t="n">
         <f aca="false">IF(F16="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
         <v>0.05</v>
       </c>
-      <c r="H16" s="26" t="n">
+      <c r="H16" s="28" t="n">
         <v>1200000</v>
       </c>
       <c r="I16" s="12" t="n">
         <f aca="false">H16/Parametros!$B$6</f>
-        <v>204.32487655372</v>
-      </c>
-      <c r="J16" s="19" t="n">
+        <v>210.748155953635</v>
+      </c>
+      <c r="J16" s="22" t="n">
         <f aca="false">H16*G16</f>
         <v>60000</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L16" s="6"/>
     </row>
@@ -2877,37 +3287,37 @@
         <v>13</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>109</v>
+        <v>158</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>144</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="G17" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="G17" s="27" t="n">
         <f aca="false">IF(F17="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
         <v>0.05</v>
       </c>
-      <c r="H17" s="26" t="n">
+      <c r="H17" s="28" t="n">
         <v>900000</v>
       </c>
       <c r="I17" s="12" t="n">
         <f aca="false">H17/Parametros!$B$6</f>
-        <v>153.24365741529</v>
-      </c>
-      <c r="J17" s="19" t="n">
+        <v>158.061116965227</v>
+      </c>
+      <c r="J17" s="22" t="n">
         <f aca="false">H17*G17</f>
         <v>45000</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L17" s="6"/>
     </row>
@@ -2916,40 +3326,40 @@
         <v>14</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>126</v>
+        <v>158</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>161</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="G18" s="25" t="n">
+        <v>161</v>
+      </c>
+      <c r="G18" s="27" t="n">
         <f aca="false">IF(F18="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
         <v>0.1</v>
       </c>
-      <c r="H18" s="26" t="n">
+      <c r="H18" s="28" t="n">
         <v>700000</v>
       </c>
       <c r="I18" s="12" t="n">
         <f aca="false">H18/Parametros!$B$6</f>
-        <v>119.189511323004</v>
-      </c>
-      <c r="J18" s="19" t="n">
+        <v>122.936424306287</v>
+      </c>
+      <c r="J18" s="22" t="n">
         <f aca="false">H18*G18</f>
         <v>70000</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>128</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2957,393 +3367,67 @@
         <v>15</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>130</v>
+        <v>158</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>165</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="G19" s="25" t="n">
+        <v>167</v>
+      </c>
+      <c r="G19" s="27" t="n">
         <f aca="false">IF(F19="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
         <v>0.1</v>
       </c>
-      <c r="H19" s="26" t="n">
+      <c r="H19" s="28" t="n">
         <v>1200000</v>
       </c>
       <c r="I19" s="12" t="n">
         <f aca="false">H19/Parametros!$B$6</f>
-        <v>204.32487655372</v>
-      </c>
-      <c r="J19" s="19" t="n">
+        <v>210.748155953635</v>
+      </c>
+      <c r="J19" s="22" t="n">
         <f aca="false">H19*G19</f>
         <v>120000</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G20" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="H20" s="27" t="n">
+        <v>169</v>
+      </c>
+      <c r="H20" s="29" t="n">
         <f aca="false">SUM(H5:H19)</f>
         <v>19550000</v>
       </c>
       <c r="I20" s="13" t="n">
         <f aca="false">SUM(I5:I19)</f>
-        <v>3328.79278052103</v>
-      </c>
-      <c r="J20" s="27" t="n">
+        <v>3433.43870741131</v>
+      </c>
+      <c r="J20" s="29" t="n">
         <f aca="false">SUM(J5:J19)</f>
         <v>1072500</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="50"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B5" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" s="21" t="n">
-        <f aca="false">COUNTIFS(Alquileres_Unidad!$E$5:$E$19,"1 dormitorio")</f>
-        <v>6</v>
-      </c>
-      <c r="D5" s="29" t="n">
-        <f aca="false">C5-B5</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="10" t="str">
-        <f aca="false">IF(D5=0,"Coincide","Revisar")</f>
-        <v>Coincide</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B6" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="C6" s="21" t="n">
-        <f aca="false">COUNTIFS(Alquileres_Unidad!$E$5:$E$19,"2 dormitorios")</f>
-        <v>6</v>
-      </c>
-      <c r="D6" s="29" t="n">
-        <f aca="false">C6-B6</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="10" t="str">
-        <f aca="false">IF(D6=0,"Coincide","Revisar")</f>
-        <v>Coincide</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B7" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="21" t="n">
-        <f aca="false">COUNTIFS(Alquileres_Unidad!$E$5:$E$19,"3 dormitorios")</f>
-        <v>1</v>
-      </c>
-      <c r="D7" s="29" t="n">
-        <f aca="false">C7-B7</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="10" t="str">
-        <f aca="false">IF(D7=0,"Coincide","Revisar")</f>
-        <v>Coincide</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B8" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="21" t="n">
-        <f aca="false">COUNTIFS(Alquileres_Unidad!$F$5:$F$19,"Local comercial")</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="29" t="n">
-        <f aca="false">C8-B8</f>
-        <v>-1</v>
-      </c>
-      <c r="E8" s="10" t="str">
-        <f aca="false">IF(D8=0,"Coincide","Revisar")</f>
-        <v>Revisar</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B9" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="21" t="n">
-        <f aca="false">COUNTIFS(Alquileres_Unidad!$F$5:$F$19,"Cochera")</f>
-        <v>1</v>
-      </c>
-      <c r="D9" s="29" t="n">
-        <f aca="false">C9-B9</f>
-        <v>1</v>
-      </c>
-      <c r="E9" s="10" t="str">
-        <f aca="false">IF(D9=0,"Coincide","Revisar")</f>
-        <v>Revisar</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B10" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="21" t="n">
-        <f aca="false">COUNTIFS(Alquileres_Unidad!$F$5:$F$19,"Cochera y departamento")</f>
-        <v>1</v>
-      </c>
-      <c r="D10" s="29" t="n">
-        <f aca="false">C10-B10</f>
-        <v>1</v>
-      </c>
-      <c r="E10" s="10" t="str">
-        <f aca="false">IF(D10=0,"Coincide","Revisar")</f>
-        <v>Revisar</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B12" s="11" t="n">
-        <f aca="false">Alquileres_Unidad!$H$20</f>
-        <v>19550000</v>
-      </c>
-      <c r="C12" s="26" t="n">
-        <v>19550000</v>
-      </c>
-      <c r="D12" s="19" t="n">
-        <f aca="false">B12-C12</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="10" t="str">
-        <f aca="false">IF(D12=0,"Suma correcta","DIFERENCIA")</f>
-        <v>Suma correcta</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B16" s="21" t="n">
-        <f aca="false">COUNTIFS(Alquileres_Unidad!$C$5:$C$19,A16)</f>
-        <v>4</v>
-      </c>
-      <c r="C16" s="19" t="n">
-        <f aca="false">SUMIFS(Alquileres_Unidad!$H$5:$H$19,Alquileres_Unidad!$C$5:$C$19,A16)</f>
-        <v>5300000</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <f aca="false">C16/Parametros!$B$6</f>
-        <v>902.434871445598</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <f aca="false">C16/$C$20</f>
-        <v>0.271099744245524</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B17" s="21" t="n">
-        <f aca="false">COUNTIFS(Alquileres_Unidad!$C$5:$C$19,A17)</f>
-        <v>5</v>
-      </c>
-      <c r="C17" s="19" t="n">
-        <f aca="false">SUMIFS(Alquileres_Unidad!$H$5:$H$19,Alquileres_Unidad!$C$5:$C$19,A17)</f>
-        <v>7350000</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <f aca="false">C17/Parametros!$B$6</f>
-        <v>1251.48986889154</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <f aca="false">C17/$C$20</f>
-        <v>0.375959079283887</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B18" s="21" t="n">
-        <f aca="false">COUNTIFS(Alquileres_Unidad!$C$5:$C$19,A18)</f>
-        <v>2</v>
-      </c>
-      <c r="C18" s="19" t="n">
-        <f aca="false">SUMIFS(Alquileres_Unidad!$H$5:$H$19,Alquileres_Unidad!$C$5:$C$19,A18)</f>
-        <v>2900000</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <f aca="false">C18/Parametros!$B$6</f>
-        <v>493.785118338158</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <f aca="false">C18/$C$20</f>
-        <v>0.148337595907928</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B19" s="21" t="n">
-        <f aca="false">COUNTIFS(Alquileres_Unidad!$C$5:$C$19,A19)</f>
-        <v>4</v>
-      </c>
-      <c r="C19" s="19" t="n">
-        <f aca="false">SUMIFS(Alquileres_Unidad!$H$5:$H$19,Alquileres_Unidad!$C$5:$C$19,A19)</f>
-        <v>4000000</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <f aca="false">C19/Parametros!$B$6</f>
-        <v>681.082921845735</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <f aca="false">C19/$C$20</f>
-        <v>0.20460358056266</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B20" s="15" t="n">
-        <f aca="false">SUM(B16:B19)</f>
-        <v>15</v>
-      </c>
-      <c r="C20" s="27" t="n">
-        <f aca="false">SUM(C16:C19)</f>
-        <v>19550000</v>
-      </c>
-      <c r="D20" s="13" t="n">
-        <f aca="false">SUM(D16:D19)</f>
-        <v>3328.79278052103</v>
-      </c>
-      <c r="E20" s="30" t="n">
-        <f aca="false">SUM(E16:E19)</f>
-        <v>1</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -3362,368 +3446,314 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="50"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="23" t="n">
+        <f aca="false">COUNTIFS(Alquileres_Unidad!$E$5:$E$19,"1 dormitorio")</f>
+        <v>6</v>
+      </c>
+      <c r="D5" s="30" t="n">
+        <f aca="false">C5-B5</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="10" t="str">
+        <f aca="false">IF(D5=0,"Coincide","Revisar")</f>
+        <v>Coincide</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="23" t="n">
+        <f aca="false">COUNTIFS(Alquileres_Unidad!$E$5:$E$19,"2 dormitorios")</f>
+        <v>6</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <f aca="false">C6-B6</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="10" t="str">
+        <f aca="false">IF(D6=0,"Coincide","Revisar")</f>
+        <v>Coincide</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <f aca="false">COUNTIFS(Alquileres_Unidad!$E$5:$E$19,"3 dormitorios")</f>
+        <v>1</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <f aca="false">C7-B7</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="10" t="str">
+        <f aca="false">IF(D7=0,"Coincide","Revisar")</f>
+        <v>Coincide</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="23" t="n">
+        <f aca="false">COUNTIFS(Alquileres_Unidad!$F$5:$F$19,"Local comercial")</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <f aca="false">C8-B8</f>
+        <v>-1</v>
+      </c>
+      <c r="E8" s="10" t="str">
+        <f aca="false">IF(D8=0,"Coincide","Revisar")</f>
+        <v>Revisar</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <f aca="false">COUNTIFS(Alquileres_Unidad!$F$5:$F$19,"Cochera")</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <f aca="false">C9-B9</f>
+        <v>1</v>
+      </c>
+      <c r="E9" s="10" t="str">
+        <f aca="false">IF(D9=0,"Coincide","Revisar")</f>
+        <v>Revisar</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="23" t="n">
+        <f aca="false">COUNTIFS(Alquileres_Unidad!$F$5:$F$19,"Cochera y departamento")</f>
+        <v>1</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <f aca="false">C10-B10</f>
+        <v>1</v>
+      </c>
+      <c r="E10" s="10" t="str">
+        <f aca="false">IF(D10=0,"Coincide","Revisar")</f>
+        <v>Revisar</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B12" s="11" t="n">
+        <f aca="false">Alquileres_Unidad!$H$20</f>
+        <v>19550000</v>
+      </c>
+      <c r="C12" s="28" t="n">
+        <v>19550000</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <f aca="false">B12-C12</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="10" t="str">
+        <f aca="false">IF(D12=0,"Suma correcta","DIFERENCIA")</f>
+        <v>Suma correcta</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B16" s="23" t="n">
+        <f aca="false">COUNTIFS(Alquileres_Unidad!$C$5:$C$19,A16)</f>
+        <v>4</v>
+      </c>
+      <c r="C16" s="22" t="n">
+        <f aca="false">SUMIFS(Alquileres_Unidad!$H$5:$H$19,Alquileres_Unidad!$C$5:$C$19,A16)</f>
+        <v>5300000</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <f aca="false">C16/Parametros!$B$6</f>
+        <v>930.80435546189</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <f aca="false">C16/$C$20</f>
+        <v>0.271099744245524</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" s="23" t="n">
+        <f aca="false">COUNTIFS(Alquileres_Unidad!$C$5:$C$19,A17)</f>
+        <v>5</v>
+      </c>
+      <c r="C17" s="22" t="n">
+        <f aca="false">SUMIFS(Alquileres_Unidad!$H$5:$H$19,Alquileres_Unidad!$C$5:$C$19,A17)</f>
+        <v>7350000</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <f aca="false">C17/Parametros!$B$6</f>
+        <v>1290.83245521602</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <f aca="false">C17/$C$20</f>
+        <v>0.375959079283887</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="31" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24" t="s">
+      <c r="B18" s="23" t="n">
+        <f aca="false">COUNTIFS(Alquileres_Unidad!$C$5:$C$19,A18)</f>
+        <v>2</v>
+      </c>
+      <c r="C18" s="22" t="n">
+        <f aca="false">SUMIFS(Alquileres_Unidad!$H$5:$H$19,Alquileres_Unidad!$C$5:$C$19,A18)</f>
+        <v>2900000</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <f aca="false">C18/Parametros!$B$6</f>
+        <v>509.308043554619</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <f aca="false">C18/$C$20</f>
+        <v>0.148337595907928</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C6" s="24"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="24"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="26" t="n">
-        <v>1500000</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" s="26" t="n">
-        <v>1500000</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" s="26" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" s="26" t="n">
-        <v>1100000</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="C12" s="24"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="26" t="n">
-        <v>1600000</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="26" t="n">
-        <v>1500000</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="26" t="n">
-        <v>1500000</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" s="26" t="n">
-        <v>1500000</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C17" s="26" t="n">
-        <v>1250000</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="24"/>
-      <c r="B18" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="C18" s="24"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C19" s="26" t="n">
-        <v>1300000</v>
+      <c r="B19" s="23" t="n">
+        <f aca="false">COUNTIFS(Alquileres_Unidad!$C$5:$C$19,A19)</f>
+        <v>4</v>
+      </c>
+      <c r="C19" s="22" t="n">
+        <f aca="false">SUMIFS(Alquileres_Unidad!$H$5:$H$19,Alquileres_Unidad!$C$5:$C$19,A19)</f>
+        <v>4000000</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <f aca="false">C19/Parametros!$B$6</f>
+        <v>702.493853178785</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <f aca="false">C19/$C$20</f>
+        <v>0.20460358056266</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="C20" s="26" t="n">
-        <v>1600000</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24"/>
-      <c r="B21" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="C21" s="24"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B22" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C22" s="26" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" s="26" t="n">
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="C24" s="26" t="n">
-        <v>700000</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B25" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="C25" s="26" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24"/>
-      <c r="B26" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="C26" s="26" t="n">
+      <c r="A20" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B20" s="19" t="n">
+        <f aca="false">SUM(B16:B19)</f>
+        <v>15</v>
+      </c>
+      <c r="C20" s="29" t="n">
+        <f aca="false">SUM(C16:C19)</f>
         <v>19550000</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="B27" s="32" t="n">
-        <v>6100</v>
-      </c>
-      <c r="C27" s="26" t="n">
-        <v>3205</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="31" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="24" t="n">
-        <v>340000</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="C32" s="24" t="n">
-        <v>3205</v>
-      </c>
-      <c r="D32" s="24" t="n">
-        <v>19550000</v>
-      </c>
-      <c r="E32" s="24" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="24"/>
-      <c r="B33" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="C33" s="24" t="n">
-        <v>2764</v>
-      </c>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="24"/>
-      <c r="B34" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="C34" s="24" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="24"/>
-      <c r="B35" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="24"/>
-      <c r="B36" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="B37" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
-        <v>182</v>
+      <c r="D20" s="13" t="n">
+        <f aca="false">SUM(D16:D19)</f>
+        <v>3433.43870741131</v>
+      </c>
+      <c r="E20" s="31" t="n">
+        <f aca="false">SUM(E16:E19)</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3742,7 +3772,387 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="32" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="26"/>
+      <c r="B6" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="C6" s="26"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="26"/>
+      <c r="B7" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="26"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="28" t="n">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="28" t="n">
+        <v>1100000</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="26"/>
+      <c r="B12" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" s="26"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="28" t="n">
+        <v>1600000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="28" t="n">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" s="28" t="n">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="28" t="n">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C17" s="28" t="n">
+        <v>1250000</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="26"/>
+      <c r="B18" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18" s="26"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="28" t="n">
+        <v>1300000</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="C20" s="28" t="n">
+        <v>1600000</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="26"/>
+      <c r="B21" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="C21" s="26"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" s="28" t="n">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C23" s="28" t="n">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="28" t="n">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" s="28" t="n">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="26"/>
+      <c r="B26" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="28" t="n">
+        <v>19550000</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="B27" s="33" t="n">
+        <v>6100</v>
+      </c>
+      <c r="C27" s="28" t="n">
+        <v>3205</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="32" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="26" t="n">
+        <v>340000</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="C32" s="26" t="n">
+        <v>3205</v>
+      </c>
+      <c r="D32" s="26" t="n">
+        <v>19550000</v>
+      </c>
+      <c r="E32" s="26" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="26"/>
+      <c r="B33" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="C33" s="26" t="n">
+        <v>2764</v>
+      </c>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="26"/>
+      <c r="B34" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="C34" s="26" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="26"/>
+      <c r="B35" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="26"/>
+      <c r="B36" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -3753,7 +4163,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3763,338 +4173,436 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>186</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="B5" s="33" t="n">
+        <v>222</v>
+      </c>
+      <c r="B5" s="34" t="n">
         <v>340000</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>189</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B6" s="32" t="n">
-        <v>5873</v>
+        <v>225</v>
+      </c>
+      <c r="B6" s="33" t="n">
+        <v>5694</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>191</v>
+        <v>226</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>192</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>194</v>
+        <v>228</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>229</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>191</v>
+        <v>226</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B8" s="32" t="n">
+        <v>231</v>
+      </c>
+      <c r="B8" s="33" t="n">
         <v>6100</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>197</v>
+        <v>232</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>198</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="B9" s="34" t="n">
+        <v>234</v>
+      </c>
+      <c r="B9" s="35" t="n">
         <v>0.05</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B10" s="34" t="n">
+        <v>236</v>
+      </c>
+      <c r="B10" s="35" t="n">
         <v>0.1</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B11" s="34" t="n">
+        <v>238</v>
+      </c>
+      <c r="B11" s="35" t="n">
         <v>0.03</v>
       </c>
-      <c r="C11" s="35" t="s">
-        <v>204</v>
+      <c r="C11" s="36" t="s">
+        <v>239</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B12" s="34" t="n">
+        <v>241</v>
+      </c>
+      <c r="B12" s="35" t="n">
         <v>0.08</v>
       </c>
-      <c r="C12" s="35" t="s">
-        <v>204</v>
+      <c r="C12" s="36" t="s">
+        <v>239</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>207</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B13" s="34" t="n">
+        <v>243</v>
+      </c>
+      <c r="B13" s="35" t="n">
         <v>0.05</v>
       </c>
-      <c r="C13" s="35" t="s">
-        <v>209</v>
+      <c r="C13" s="36" t="s">
+        <v>244</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>210</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B14" s="33" t="n">
+        <v>246</v>
+      </c>
+      <c r="B14" s="34" t="n">
         <v>1200</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="B15" s="34" t="n">
+        <v>248</v>
+      </c>
+      <c r="B15" s="35" t="n">
         <v>0.1</v>
       </c>
-      <c r="C15" s="35" t="s">
-        <v>214</v>
+      <c r="C15" s="36" t="s">
+        <v>249</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>215</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B16" s="36" t="n">
+        <v>251</v>
+      </c>
+      <c r="B16" s="37" t="n">
         <v>0.015</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>217</v>
+        <v>252</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B17" s="36" t="n">
+        <v>253</v>
+      </c>
+      <c r="B17" s="37" t="n">
         <v>0.03</v>
       </c>
-      <c r="C17" s="35" t="s">
-        <v>219</v>
+      <c r="C17" s="36" t="s">
+        <v>254</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>220</v>
+        <v>255</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="B18" s="36" t="n">
+        <v>256</v>
+      </c>
+      <c r="B18" s="37" t="n">
         <v>0.05</v>
       </c>
-      <c r="C18" s="35" t="s">
-        <v>219</v>
+      <c r="C18" s="36" t="s">
+        <v>254</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>222</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="B19" s="36" t="n">
+        <v>258</v>
+      </c>
+      <c r="B19" s="37" t="n">
         <v>0.08</v>
       </c>
-      <c r="C19" s="35" t="s">
-        <v>219</v>
+      <c r="C19" s="36" t="s">
+        <v>254</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>224</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="B20" s="36" t="n">
+        <v>260</v>
+      </c>
+      <c r="B20" s="37" t="n">
         <v>0.02</v>
       </c>
-      <c r="C20" s="35" t="s">
-        <v>219</v>
+      <c r="C20" s="36" t="s">
+        <v>254</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>226</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B21" s="36" t="n">
+        <v>262</v>
+      </c>
+      <c r="B21" s="37" t="n">
         <v>0.035</v>
       </c>
-      <c r="C21" s="35" t="s">
-        <v>219</v>
+      <c r="C21" s="36" t="s">
+        <v>254</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>226</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B22" s="36" t="n">
+        <v>263</v>
+      </c>
+      <c r="B22" s="37" t="n">
         <v>0.05</v>
       </c>
-      <c r="C22" s="35" t="s">
-        <v>219</v>
+      <c r="C22" s="36" t="s">
+        <v>254</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B23" s="26" t="n">
-        <v>2500000</v>
+        <v>264</v>
+      </c>
+      <c r="B23" s="28" t="n">
+        <v>3000000</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>231</v>
+        <v>266</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="B24" s="26" t="n">
-        <v>3000000</v>
+        <v>267</v>
+      </c>
+      <c r="B24" s="28" t="n">
+        <v>3200000</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B25" s="26" t="n">
+        <v>269</v>
+      </c>
+      <c r="B25" s="28" t="n">
         <v>2100000</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>235</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B26" s="26" t="n">
-        <v>4200000</v>
+        <v>271</v>
+      </c>
+      <c r="B26" s="28" t="n">
+        <v>6300000</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B27" s="26" t="n">
+        <v>272</v>
+      </c>
+      <c r="B27" s="28" t="n">
         <v>2700000</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>238</v>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B28" s="38" t="n">
+        <v>11</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B29" s="38" t="n">
+        <v>31</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B30" s="33" t="n">
+        <v>340</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="33" t="n">
+        <v>1109</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B32" s="34" t="n">
+        <v>650</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B33" s="34" t="n">
+        <v>650000</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B34" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/projects/edificio-ciudad-nueva/entregables/Edificio_Ciudad_Nueva_Alquileres_Rentabilidad.xlsx
+++ b/projects/edificio-ciudad-nueva/entregables/Edificio_Ciudad_Nueva_Alquileres_Rentabilidad.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="288">
   <si>
     <t xml:space="preserve">Rentabilidad sobre el precio — tipo de cambio del día</t>
   </si>
@@ -282,7 +282,19 @@
     <t xml:space="preserve">Ingreso bruto anual / m² construidos.</t>
   </si>
   <si>
-    <t xml:space="preserve">Referencias, no tasación: el edificio es usado (antigüedad no informada) y el costo de reposición no descuenta depreciación. El comparable es un precio de oferta sin superficie publicada.</t>
+    <t xml:space="preserve">Año de construcción</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informado por el founder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antigüedad en 2026 (años)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Año del análisis − año de construcción.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencias, no tasación: el edificio es de 1990 y el costo de reposición no descuenta depreciación ni estado de conservación. El comparable es un precio de oferta sin superficie publicada.</t>
   </si>
   <si>
     <t xml:space="preserve">Proyección de alquiler a 5 años — tres escenarios (USD, TC del día constante)</t>
@@ -702,7 +714,7 @@
     <t xml:space="preserve">Dato confirmado</t>
   </si>
   <si>
-    <t xml:space="preserve">Founder (WEB ID 143028006-118).</t>
+    <t xml:space="preserve">Founder.</t>
   </si>
   <si>
     <t xml:space="preserve">Tipo de cambio del día (Gs por USD)</t>
@@ -1123,6 +1135,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="173" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="173" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1136,10 +1152,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1920,7 +1932,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="62"/>
@@ -2073,7 +2085,7 @@
         <v>80</v>
       </c>
       <c r="B15" s="16" t="n">
-        <f aca="false">Parametros!$B$33/Parametros!$B$34</f>
+        <f aca="false">Parametros!$B$34/Parametros!$B$35</f>
         <v>72222.2222222222</v>
       </c>
       <c r="C15" s="6" t="s">
@@ -2092,9 +2104,33 @@
         <v>83</v>
       </c>
     </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="19" t="n">
+        <f aca="false">Parametros!$B$33</f>
+        <v>1990</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>84</v>
+      <c r="A18" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="19" t="n">
+        <f aca="false">2026-Parametros!$B$33</f>
+        <v>36</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2122,7 +2158,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2132,29 +2168,29 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="n">
+      <c r="A5" s="20" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="16" t="n">
@@ -2183,7 +2219,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="n">
+      <c r="A6" s="20" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="16" t="n">
@@ -2212,7 +2248,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="20" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="16" t="n">
@@ -2241,7 +2277,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="n">
+      <c r="A8" s="20" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="16" t="n">
@@ -2270,7 +2306,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="20" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="16" t="n">
@@ -2300,86 +2336,86 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B10" s="20" t="n">
+        <v>97</v>
+      </c>
+      <c r="B10" s="21" t="n">
         <f aca="false">SUM(B5:B9)</f>
         <v>218743.10871549</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="21" t="n">
         <f aca="false">SUM(C5:C9)</f>
         <v>149169.69884939</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="21" t="n">
         <f aca="false">SUM(D5:D9)</f>
         <v>227662.994599579</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="21" t="n">
         <f aca="false">SUM(E5:E9)</f>
         <v>155472.727470364</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="21" t="n">
         <f aca="false">SUM(F5:F9)</f>
         <v>241711.377804004</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="21" t="n">
         <f aca="false">SUM(G5:G9)</f>
         <v>165399.688708046</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" s="21" t="n">
+        <v>98</v>
+      </c>
+      <c r="B11" s="22" t="n">
         <f aca="false">Parametros!$B$17</f>
         <v>0.03</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="22" t="n">
         <f aca="false">Parametros!$B$18</f>
         <v>0.05</v>
       </c>
-      <c r="F11" s="21" t="n">
+      <c r="F11" s="22" t="n">
         <f aca="false">Parametros!$B$19</f>
         <v>0.08</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B16" s="22" t="n">
+        <v>107</v>
+      </c>
+      <c r="B16" s="23" t="n">
         <f aca="false">AVERAGEIFS(Alquileres_Unidad!$H$5:$H$19,Alquileres_Unidad!$E$5:$E$19,"1 dormitorio")</f>
         <v>1158333.33333333</v>
       </c>
@@ -2395,16 +2431,16 @@
         <f aca="false">C16/B16-1</f>
         <v>1.58992805755396</v>
       </c>
-      <c r="F16" s="23" t="n">
+      <c r="F16" s="19" t="n">
         <f aca="false">COUNTIFS(Alquileres_Unidad!$E$5:$E$19,"1 dormitorio")</f>
         <v>6</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B17" s="22" t="n">
+        <v>108</v>
+      </c>
+      <c r="B17" s="23" t="n">
         <f aca="false">AVERAGEIFS(Alquileres_Unidad!$H$5:$H$19,Alquileres_Unidad!$E$5:$E$19,"2 dormitorios")</f>
         <v>1516666.66666667</v>
       </c>
@@ -2420,14 +2456,14 @@
         <f aca="false">C17/B17-1</f>
         <v>0.384615384615385</v>
       </c>
-      <c r="F17" s="23" t="n">
+      <c r="F17" s="19" t="n">
         <f aca="false">COUNTIFS(Alquileres_Unidad!$E$5:$E$19,"2 dormitorios")</f>
         <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C18" s="11" t="n">
         <f aca="false">Parametros!$B$27</f>
@@ -2436,7 +2472,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2464,7 +2500,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2477,35 +2513,35 @@
         <v>32</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B5" s="21" t="n">
+        <v>115</v>
+      </c>
+      <c r="B5" s="22" t="n">
         <f aca="false">Parametros!$B$20</f>
         <v>0.02</v>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="C5" s="22" t="n">
         <f aca="false">Parametros!$B$21</f>
         <v>0.035</v>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D5" s="22" t="n">
         <f aca="false">Parametros!$B$22</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B6" s="16" t="n">
         <f aca="false">Parametros!$B$5*(1+B5)^5</f>
@@ -2522,7 +2558,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">B6-Parametros!$B$5</f>
@@ -2539,7 +2575,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B8" s="16" t="n">
         <f aca="false">-B6*Parametros!$B$16</f>
@@ -2556,7 +2592,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B9" s="24" t="n">
         <f aca="false">Proyeccion!C10</f>
@@ -2573,24 +2609,24 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B10" s="20" t="n">
+        <v>120</v>
+      </c>
+      <c r="B10" s="21" t="n">
         <f aca="false">B7+B8+B9</f>
         <v>178926.35984107</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="21" t="n">
         <f aca="false">C7+C8+C9</f>
         <v>213228.871231502</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="21" t="n">
         <f aca="false">D7+D8+D9</f>
         <v>252826.383989297</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B11" s="14" t="n">
         <f aca="false">B10/Parametros!$B$5</f>
@@ -2607,12 +2643,12 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B14" s="16" t="n">
         <f aca="false">-Parametros!$B$5</f>
@@ -2629,7 +2665,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B15" s="16" t="n">
         <f aca="false">Proyeccion!C5</f>
@@ -2646,7 +2682,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B16" s="16" t="n">
         <f aca="false">Proyeccion!C6</f>
@@ -2663,7 +2699,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B17" s="16" t="n">
         <f aca="false">Proyeccion!C7</f>
@@ -2680,7 +2716,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B18" s="16" t="n">
         <f aca="false">Proyeccion!C8</f>
@@ -2697,7 +2733,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B19" s="16" t="n">
         <f aca="false">Proyeccion!C9+B6+B8</f>
@@ -2714,7 +2750,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B20" s="25" t="n">
         <f aca="false">IRR(B14:B19)</f>
@@ -2731,7 +2767,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2768,7 +2804,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2778,37 +2814,37 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>32</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>15</v>
@@ -2819,19 +2855,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G5" s="27" t="n">
         <f aca="false">IF(F5="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
@@ -2844,12 +2880,12 @@
         <f aca="false">H5/Parametros!$B$6</f>
         <v>263.435194942044</v>
       </c>
-      <c r="J5" s="22" t="n">
+      <c r="J5" s="23" t="n">
         <f aca="false">H5*G5</f>
         <v>75000</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L5" s="6"/>
     </row>
@@ -2858,19 +2894,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>138</v>
-      </c>
       <c r="D6" s="26" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G6" s="27" t="n">
         <f aca="false">IF(F6="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
@@ -2883,12 +2919,12 @@
         <f aca="false">H6/Parametros!$B$6</f>
         <v>263.435194942044</v>
       </c>
-      <c r="J6" s="22" t="n">
+      <c r="J6" s="23" t="n">
         <f aca="false">H6*G6</f>
         <v>75000</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L6" s="6"/>
     </row>
@@ -2897,19 +2933,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D7" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>144</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>140</v>
       </c>
       <c r="G7" s="27" t="n">
         <f aca="false">IF(F7="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
@@ -2922,12 +2958,12 @@
         <f aca="false">H7/Parametros!$B$6</f>
         <v>210.748155953635</v>
       </c>
-      <c r="J7" s="22" t="n">
+      <c r="J7" s="23" t="n">
         <f aca="false">H7*G7</f>
         <v>60000</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L7" s="6"/>
     </row>
@@ -2936,19 +2972,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D8" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>144</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>140</v>
       </c>
       <c r="G8" s="27" t="n">
         <f aca="false">IF(F8="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
@@ -2961,12 +2997,12 @@
         <f aca="false">H8/Parametros!$B$6</f>
         <v>193.185809624166</v>
       </c>
-      <c r="J8" s="22" t="n">
+      <c r="J8" s="23" t="n">
         <f aca="false">H8*G8</f>
         <v>55000</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L8" s="6"/>
     </row>
@@ -2975,19 +3011,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G9" s="27" t="n">
         <f aca="false">IF(F9="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
@@ -3000,12 +3036,12 @@
         <f aca="false">H9/Parametros!$B$6</f>
         <v>280.997541271514</v>
       </c>
-      <c r="J9" s="22" t="n">
+      <c r="J9" s="23" t="n">
         <f aca="false">H9*G9</f>
         <v>80000</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L9" s="6"/>
     </row>
@@ -3014,19 +3050,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G10" s="27" t="n">
         <f aca="false">IF(F10="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
@@ -3039,12 +3075,12 @@
         <f aca="false">H10/Parametros!$B$6</f>
         <v>263.435194942044</v>
       </c>
-      <c r="J10" s="22" t="n">
+      <c r="J10" s="23" t="n">
         <f aca="false">H10*G10</f>
         <v>75000</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L10" s="6"/>
     </row>
@@ -3053,19 +3089,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G11" s="27" t="n">
         <f aca="false">IF(F11="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
@@ -3078,12 +3114,12 @@
         <f aca="false">H11/Parametros!$B$6</f>
         <v>263.435194942044</v>
       </c>
-      <c r="J11" s="22" t="n">
+      <c r="J11" s="23" t="n">
         <f aca="false">H11*G11</f>
         <v>75000</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L11" s="6"/>
     </row>
@@ -3092,19 +3128,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G12" s="27" t="n">
         <f aca="false">IF(F12="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
@@ -3117,12 +3153,12 @@
         <f aca="false">H12/Parametros!$B$6</f>
         <v>263.435194942044</v>
       </c>
-      <c r="J12" s="22" t="n">
+      <c r="J12" s="23" t="n">
         <f aca="false">H12*G12</f>
         <v>75000</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L12" s="6"/>
     </row>
@@ -3131,19 +3167,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>147</v>
-      </c>
       <c r="D13" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F13" s="10" t="s">
         <v>144</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>140</v>
       </c>
       <c r="G13" s="27" t="n">
         <f aca="false">IF(F13="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
@@ -3156,12 +3192,12 @@
         <f aca="false">H13/Parametros!$B$6</f>
         <v>219.52932911837</v>
       </c>
-      <c r="J13" s="22" t="n">
+      <c r="J13" s="23" t="n">
         <f aca="false">H13*G13</f>
         <v>62500</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L13" s="6"/>
     </row>
@@ -3170,19 +3206,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D14" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F14" s="10" t="s">
         <v>144</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>140</v>
       </c>
       <c r="G14" s="27" t="n">
         <f aca="false">IF(F14="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
@@ -3195,12 +3231,12 @@
         <f aca="false">H14/Parametros!$B$6</f>
         <v>228.310502283105</v>
       </c>
-      <c r="J14" s="22" t="n">
+      <c r="J14" s="23" t="n">
         <f aca="false">H14*G14</f>
         <v>65000</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L14" s="6"/>
     </row>
@@ -3209,19 +3245,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G15" s="27" t="n">
         <f aca="false">IF(F15="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
@@ -3234,12 +3270,12 @@
         <f aca="false">H15/Parametros!$B$6</f>
         <v>280.997541271514</v>
       </c>
-      <c r="J15" s="22" t="n">
+      <c r="J15" s="23" t="n">
         <f aca="false">H15*G15</f>
         <v>80000</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L15" s="6"/>
     </row>
@@ -3248,19 +3284,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D16" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F16" s="10" t="s">
         <v>144</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>140</v>
       </c>
       <c r="G16" s="27" t="n">
         <f aca="false">IF(F16="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
@@ -3273,12 +3309,12 @@
         <f aca="false">H16/Parametros!$B$6</f>
         <v>210.748155953635</v>
       </c>
-      <c r="J16" s="22" t="n">
+      <c r="J16" s="23" t="n">
         <f aca="false">H16*G16</f>
         <v>60000</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L16" s="6"/>
     </row>
@@ -3287,19 +3323,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D17" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>144</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>140</v>
       </c>
       <c r="G17" s="27" t="n">
         <f aca="false">IF(F17="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
@@ -3312,12 +3348,12 @@
         <f aca="false">H17/Parametros!$B$6</f>
         <v>158.061116965227</v>
       </c>
-      <c r="J17" s="22" t="n">
+      <c r="J17" s="23" t="n">
         <f aca="false">H17*G17</f>
         <v>45000</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L17" s="6"/>
     </row>
@@ -3326,19 +3362,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G18" s="27" t="n">
         <f aca="false">IF(F18="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
@@ -3351,15 +3387,15 @@
         <f aca="false">H18/Parametros!$B$6</f>
         <v>122.936424306287</v>
       </c>
-      <c r="J18" s="22" t="n">
+      <c r="J18" s="23" t="n">
         <f aca="false">H18*G18</f>
         <v>70000</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3367,19 +3403,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G19" s="27" t="n">
         <f aca="false">IF(F19="Departamento",Parametros!$B$9,Parametros!$B$10)</f>
@@ -3392,20 +3428,20 @@
         <f aca="false">H19/Parametros!$B$6</f>
         <v>210.748155953635</v>
       </c>
-      <c r="J19" s="22" t="n">
+      <c r="J19" s="23" t="n">
         <f aca="false">H19*G19</f>
         <v>120000</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G20" s="4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H20" s="29" t="n">
         <f aca="false">SUM(H5:H19)</f>
@@ -3422,12 +3458,12 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3457,7 +3493,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3470,16 +3506,16 @@
         <v>32</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>15</v>
@@ -3487,12 +3523,12 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="23" t="n">
+      <c r="C5" s="19" t="n">
         <f aca="false">COUNTIFS(Alquileres_Unidad!$E$5:$E$19,"1 dormitorio")</f>
         <v>6</v>
       </c>
@@ -3507,12 +3543,12 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="19" t="n">
         <f aca="false">COUNTIFS(Alquileres_Unidad!$E$5:$E$19,"2 dormitorios")</f>
         <v>6</v>
       </c>
@@ -3527,12 +3563,12 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B7" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="19" t="n">
         <f aca="false">COUNTIFS(Alquileres_Unidad!$E$5:$E$19,"3 dormitorios")</f>
         <v>1</v>
       </c>
@@ -3547,12 +3583,12 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B8" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="19" t="n">
         <f aca="false">COUNTIFS(Alquileres_Unidad!$F$5:$F$19,"Local comercial")</f>
         <v>0</v>
       </c>
@@ -3565,17 +3601,17 @@
         <v>Revisar</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B9" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="19" t="n">
         <f aca="false">COUNTIFS(Alquileres_Unidad!$F$5:$F$19,"Cochera")</f>
         <v>1</v>
       </c>
@@ -3590,12 +3626,12 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C10" s="19" t="n">
         <f aca="false">COUNTIFS(Alquileres_Unidad!$F$5:$F$19,"Cochera y departamento")</f>
         <v>1</v>
       </c>
@@ -3610,7 +3646,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">Alquileres_Unidad!$H$20</f>
@@ -3619,7 +3655,7 @@
       <c r="C12" s="28" t="n">
         <v>19550000</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="23" t="n">
         <f aca="false">B12-C12</f>
         <v>0</v>
       </c>
@@ -3630,36 +3666,36 @@
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B16" s="23" t="n">
+        <v>142</v>
+      </c>
+      <c r="B16" s="19" t="n">
         <f aca="false">COUNTIFS(Alquileres_Unidad!$C$5:$C$19,A16)</f>
         <v>4</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="23" t="n">
         <f aca="false">SUMIFS(Alquileres_Unidad!$H$5:$H$19,Alquileres_Unidad!$C$5:$C$19,A16)</f>
         <v>5300000</v>
       </c>
@@ -3674,13 +3710,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B17" s="23" t="n">
+        <v>151</v>
+      </c>
+      <c r="B17" s="19" t="n">
         <f aca="false">COUNTIFS(Alquileres_Unidad!$C$5:$C$19,A17)</f>
         <v>5</v>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="23" t="n">
         <f aca="false">SUMIFS(Alquileres_Unidad!$H$5:$H$19,Alquileres_Unidad!$C$5:$C$19,A17)</f>
         <v>7350000</v>
       </c>
@@ -3695,13 +3731,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B18" s="23" t="n">
+        <v>157</v>
+      </c>
+      <c r="B18" s="19" t="n">
         <f aca="false">COUNTIFS(Alquileres_Unidad!$C$5:$C$19,A18)</f>
         <v>2</v>
       </c>
-      <c r="C18" s="22" t="n">
+      <c r="C18" s="23" t="n">
         <f aca="false">SUMIFS(Alquileres_Unidad!$H$5:$H$19,Alquileres_Unidad!$C$5:$C$19,A18)</f>
         <v>2900000</v>
       </c>
@@ -3716,13 +3752,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B19" s="23" t="n">
+        <v>162</v>
+      </c>
+      <c r="B19" s="19" t="n">
         <f aca="false">COUNTIFS(Alquileres_Unidad!$C$5:$C$19,A19)</f>
         <v>4</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="23" t="n">
         <f aca="false">SUMIFS(Alquileres_Unidad!$H$5:$H$19,Alquileres_Unidad!$C$5:$C$19,A19)</f>
         <v>4000000</v>
       </c>
@@ -3737,9 +3773,9 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="B20" s="19" t="n">
+        <v>190</v>
+      </c>
+      <c r="B20" s="20" t="n">
         <f aca="false">SUM(B16:B19)</f>
         <v>15</v>
       </c>
@@ -3782,50 +3818,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26"/>
       <c r="B6" s="26" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C6" s="26"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26"/>
       <c r="B7" s="26" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C7" s="26"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C8" s="28" t="n">
         <v>1500000</v>
@@ -3833,10 +3869,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C9" s="28" t="n">
         <v>1500000</v>
@@ -3844,10 +3880,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C10" s="28" t="n">
         <v>1200000</v>
@@ -3855,10 +3891,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C11" s="28" t="n">
         <v>1100000</v>
@@ -3867,16 +3903,16 @@
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26"/>
       <c r="B12" s="26" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C12" s="26"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C13" s="28" t="n">
         <v>1600000</v>
@@ -3884,10 +3920,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C14" s="28" t="n">
         <v>1500000</v>
@@ -3895,10 +3931,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C15" s="28" t="n">
         <v>1500000</v>
@@ -3906,10 +3942,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C16" s="28" t="n">
         <v>1500000</v>
@@ -3917,10 +3953,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C17" s="28" t="n">
         <v>1250000</v>
@@ -3929,16 +3965,16 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="26"/>
       <c r="B18" s="26" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C18" s="26"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C19" s="28" t="n">
         <v>1300000</v>
@@ -3946,10 +3982,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C20" s="28" t="n">
         <v>1600000</v>
@@ -3958,16 +3994,16 @@
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="26"/>
       <c r="B21" s="26" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C21" s="26"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C22" s="28" t="n">
         <v>1200000</v>
@@ -3975,10 +4011,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C23" s="28" t="n">
         <v>900000</v>
@@ -3986,10 +4022,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C24" s="28" t="n">
         <v>700000</v>
@@ -3997,10 +4033,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C25" s="28" t="n">
         <v>1200000</v>
@@ -4009,7 +4045,7 @@
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="26"/>
       <c r="B26" s="26" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C26" s="28" t="n">
         <v>19550000</v>
@@ -4017,7 +4053,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="26" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B27" s="33" t="n">
         <v>6100</v>
@@ -4028,29 +4064,29 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="32" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4058,7 +4094,7 @@
         <v>340000</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C32" s="26" t="n">
         <v>3205</v>
@@ -4067,73 +4103,73 @@
         <v>19550000</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="26"/>
       <c r="B33" s="26" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C33" s="26" t="n">
         <v>2764</v>
       </c>
       <c r="D33" s="26"/>
       <c r="E33" s="26" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="26"/>
       <c r="B34" s="26" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C34" s="26" t="n">
         <v>1200</v>
       </c>
       <c r="D34" s="26"/>
       <c r="E34" s="26" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="26"/>
       <c r="B35" s="26" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
       <c r="E35" s="26" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="26"/>
       <c r="B36" s="26" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D36" s="26"/>
       <c r="E36" s="26"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="26" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C37" s="26"/>
       <c r="D37" s="26"/>
       <c r="E37" s="26" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -4152,7 +4188,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -4163,7 +4199,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4173,380 +4209,380 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B5" s="34" t="n">
         <v>340000</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B6" s="33" t="n">
         <v>5694</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B8" s="33" t="n">
         <v>6100</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B9" s="35" t="n">
         <v>0.05</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B10" s="35" t="n">
         <v>0.1</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B11" s="35" t="n">
         <v>0.03</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B12" s="35" t="n">
         <v>0.08</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B13" s="35" t="n">
         <v>0.05</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B14" s="34" t="n">
         <v>1200</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B15" s="35" t="n">
         <v>0.1</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B16" s="37" t="n">
         <v>0.015</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B17" s="37" t="n">
         <v>0.03</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B18" s="37" t="n">
         <v>0.05</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B19" s="37" t="n">
         <v>0.08</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B20" s="37" t="n">
         <v>0.02</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B21" s="37" t="n">
         <v>0.035</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B22" s="37" t="n">
         <v>0.05</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B23" s="28" t="n">
         <v>3000000</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B24" s="28" t="n">
         <v>3200000</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B25" s="28" t="n">
         <v>2100000</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B26" s="28" t="n">
         <v>6300000</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B27" s="28" t="n">
         <v>2700000</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B28" s="38" t="n">
         <v>11</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B29" s="38" t="n">
         <v>31</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B30" s="33" t="n">
         <v>340</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4557,52 +4593,66 @@
         <v>1109</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B32" s="34" t="n">
         <v>650</v>
       </c>
       <c r="C32" s="36" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="B33" s="34" t="n">
+        <v>84</v>
+      </c>
+      <c r="B33" s="18" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B34" s="34" t="n">
         <v>650000</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="B34" s="18" t="n">
+      <c r="C34" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B35" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>268</v>
+      <c r="C35" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>
